--- a/config/auto_configs/2025_Hyundai_Hyundai_Tucson(NX4)_G 2.5 GDI THETA3.xlsx
+++ b/config/auto_configs/2025_Hyundai_Hyundai_Tucson(NX4)_G 2.5 GDI THETA3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_10675</t>
+          <t>HMA_10701</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_HK_01046</t>
+          <t>HMA_10674</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B132600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_HK_01046</t>
+          <t>HMA_10675</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B132700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B132800</t>
+          <t>B132600</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B132900</t>
+          <t>B132700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B133000</t>
+          <t>B132800</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B133100</t>
+          <t>B132900</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B133200</t>
+          <t>B133000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B133300</t>
+          <t>B133100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B133400</t>
+          <t>B133200</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B133500</t>
+          <t>B133300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B134600</t>
+          <t>B133400</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B134700</t>
+          <t>B133500</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B134800</t>
+          <t>B134600</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B134900</t>
+          <t>B134700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B135200</t>
+          <t>B134800</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B135300</t>
+          <t>B134900</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B135400</t>
+          <t>B135200</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B135500</t>
+          <t>B135300</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B136100</t>
+          <t>B135400</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B136200</t>
+          <t>B135500</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B136300</t>
+          <t>B136100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B136400</t>
+          <t>B136200</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B136700</t>
+          <t>B136300</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B136800</t>
+          <t>B136400</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B136900</t>
+          <t>B136700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B137000</t>
+          <t>B136800</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B137800</t>
+          <t>B136900</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B137900</t>
+          <t>B137000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B138000</t>
+          <t>B137800</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B138100</t>
+          <t>B137900</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B138200</t>
+          <t>B138000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B138300</t>
+          <t>B138100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B138400</t>
+          <t>B138200</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B138500</t>
+          <t>B138300</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B140000</t>
+          <t>B138400</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B140100</t>
+          <t>B138500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B140200</t>
+          <t>B140000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B140300</t>
+          <t>B140100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B140400</t>
+          <t>B140200</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B140500</t>
+          <t>B140300</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B140900</t>
+          <t>B140400</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B141000</t>
+          <t>B140500</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B141200</t>
+          <t>B140900</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B141300</t>
+          <t>B141000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B141400</t>
+          <t>B141200</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B141500</t>
+          <t>B141300</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B141600</t>
+          <t>B141400</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B141700</t>
+          <t>B141500</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B141800</t>
+          <t>B141600</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B141900</t>
+          <t>B141700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B145100</t>
+          <t>B141800</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B145200</t>
+          <t>B141900</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B145400</t>
+          <t>B145100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B145500</t>
+          <t>B145200</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B147300</t>
+          <t>B145400</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B147400</t>
+          <t>B145500</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B147500</t>
+          <t>B147300</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B147600</t>
+          <t>B147400</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B147700</t>
+          <t>B147500</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B147800</t>
+          <t>B147600</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B147900</t>
+          <t>B147700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B148000</t>
+          <t>B147800</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B148100</t>
+          <t>B147900</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B148200</t>
+          <t>B148000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B148300</t>
+          <t>B148100</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B148400</t>
+          <t>B148200</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B148500</t>
+          <t>B148300</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B148600</t>
+          <t>B148400</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B148700</t>
+          <t>B148500</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B148800</t>
+          <t>B148600</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B149000</t>
+          <t>B148700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B149300</t>
+          <t>B148800</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B149400</t>
+          <t>B149000</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B151100</t>
+          <t>B149300</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B151200</t>
+          <t>B149400</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B151300</t>
+          <t>B151100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B151400</t>
+          <t>B151200</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B151500</t>
+          <t>B151300</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B151600</t>
+          <t>B151400</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B162000</t>
+          <t>B151500</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B165000</t>
+          <t>B151600</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B165100</t>
+          <t>B162000</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B165200</t>
+          <t>B165000</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B165800</t>
+          <t>B165100</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B167000</t>
+          <t>B165200</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B167600</t>
+          <t>B165800</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B167700</t>
+          <t>B167000</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B167800</t>
+          <t>B167600</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B168400</t>
+          <t>B167700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B16D000</t>
+          <t>B167800</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B16D100</t>
+          <t>B168400</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B16D200</t>
+          <t>B16D000</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B16D300</t>
+          <t>B16D100</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B16DC00</t>
+          <t>B16D200</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B173000</t>
+          <t>B16D300</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B173100</t>
+          <t>B16DC00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B173200</t>
+          <t>B173000</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B173300</t>
+          <t>B173100</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B173800</t>
+          <t>B173200</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B173900</t>
+          <t>B173300</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B174000</t>
+          <t>B173800</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B174100</t>
+          <t>B173900</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B174200</t>
+          <t>B174000</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B174400</t>
+          <t>B174100</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B174500</t>
+          <t>B174200</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B174600</t>
+          <t>B174400</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B174700</t>
+          <t>B174500</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B174800</t>
+          <t>B174600</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B176200</t>
+          <t>B174700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B250200</t>
+          <t>B174800</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B261300</t>
+          <t>B176200</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B261500</t>
+          <t>B250200</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3016,10 +3016,1088 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>B261300</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HMA_HK_01046</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>B261500</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>HMA_HK_01046</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>B261600</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>BDC-TPMS</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>HMA_10661</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>4WD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HMA_HK_01049</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HMA_10642</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HMA_10665</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HMA_10666</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HMA_10645</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BDC-BCM</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HMA_10657</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BDC-IAU</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HMA_10659</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BDC-IMM</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>HMA_10658</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>BDC-SKU</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>HMA_10660</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CCNC</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>HMA_10656</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CCU_CCNF</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HMA_10653</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CCU_CGW</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>HMA_10654</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>CDCU</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HMA_10671</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HMA_HK_00980</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>DAU</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>HMA_10648</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>DCU</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HMA_10655</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DHS_FL</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HMA_10650</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>DHS_FR</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HMA_10651</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>DPSS</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HMA_10662</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HMA_HK_01018</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HMA_10646</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FPM</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HMA_10673</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HMA_HK_01057</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HMA_HK_01058</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ICC</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HMA_10652</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ILCU-LH</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HMA_10667</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ILCU-RH</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HMA_10668</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MKBD</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>HMA_10664</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HMA_10647</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HMA_10644</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>P_LBM</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HMA_10672</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PDC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HMA_10663</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HMA_HK_01066</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HMA_HK_01067</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>RCR-L</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HMA_HK_01068</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>RCR-R</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HMA_HK_01069</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HMA_10649</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HMA_10676</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SCU</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HMA_HK_01071</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>HMA_HK_01072</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HMA_HK_01073</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SWRC</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>HMA_10643</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HMA_HK_01074</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>UWB_BLE-M</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HMA_10669</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>UWB_BLE-S</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>HMA_10670</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HMA_HK_01075</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
         <is>
           <t>00</t>
         </is>
